--- a/backend/data/financials_by_company/1995.HK.xlsx
+++ b/backend/data/financials_by_company/1995.HK.xlsx
@@ -657,570 +657,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-7059534.771645</v>
+        <v>12159521</v>
       </c>
       <c r="C2" t="n">
-        <v>0.221406</v>
+        <v>0.223</v>
       </c>
       <c r="D2" t="n">
-        <v>879519000</v>
+        <v>913810000</v>
       </c>
       <c r="E2" t="n">
-        <v>-31885000</v>
+        <v>54527000</v>
       </c>
       <c r="F2" t="n">
-        <v>-31885000</v>
+        <v>54527000</v>
       </c>
       <c r="G2" t="n">
-        <v>477996000</v>
+        <v>617014000</v>
       </c>
       <c r="H2" t="n">
-        <v>85014000</v>
+        <v>73438000</v>
       </c>
       <c r="I2" t="n">
-        <v>5492483000</v>
+        <v>3402951000</v>
       </c>
       <c r="J2" t="n">
-        <v>847634000</v>
+        <v>968337000</v>
       </c>
       <c r="K2" t="n">
-        <v>762620000</v>
+        <v>894899000</v>
       </c>
       <c r="L2" t="n">
-        <v>18628000</v>
+        <v>36167000</v>
       </c>
       <c r="M2" t="n">
-        <v>3165000</v>
+        <v>3486000</v>
       </c>
       <c r="N2" t="n">
-        <v>21793000</v>
+        <v>39653000</v>
       </c>
       <c r="O2" t="n">
-        <v>502821465.228355</v>
+        <v>574646521</v>
       </c>
       <c r="P2" t="n">
-        <v>477996000</v>
+        <v>617014000</v>
       </c>
       <c r="Q2" t="n">
-        <v>6060086000</v>
+        <v>3894653000</v>
       </c>
       <c r="R2" t="n">
-        <v>1732820000</v>
+        <v>1684301000</v>
       </c>
       <c r="S2" t="n">
-        <v>1732820000</v>
+        <v>1684301000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2758</v>
+        <v>0.3663</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2758</v>
+        <v>0.3663</v>
       </c>
       <c r="V2" t="n">
-        <v>477996000</v>
+        <v>617014000</v>
       </c>
       <c r="W2" t="n">
-        <v>477996000</v>
+        <v>617014000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>477996000</v>
+        <v>617014000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-113311000</v>
+        <v>-75521000</v>
       </c>
       <c r="AA2" t="n">
-        <v>591307000</v>
+        <v>692535000</v>
       </c>
       <c r="AB2" t="n">
-        <v>591307000</v>
+        <v>692535000</v>
       </c>
       <c r="AC2" t="n">
-        <v>168148000</v>
+        <v>198878000</v>
       </c>
       <c r="AD2" t="n">
-        <v>759455000</v>
+        <v>891413000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1090000</v>
+        <v>3399000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1315000</v>
+        <v>43000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1315000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-43000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>62220000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>18628000</v>
+        <v>36167000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3165000</v>
+        <v>3486000</v>
       </c>
       <c r="AK2" t="n">
-        <v>21793000</v>
+        <v>39653000</v>
       </c>
       <c r="AL2" t="n">
-        <v>781049000</v>
+        <v>808163000</v>
       </c>
       <c r="AM2" t="n">
-        <v>567603000</v>
+        <v>491702000</v>
       </c>
       <c r="AN2" t="n">
-        <v>74150000</v>
+        <v>62220000</v>
       </c>
       <c r="AO2" t="n">
-        <v>516705000</v>
+        <v>464920000</v>
       </c>
       <c r="AP2" t="n">
-        <v>101764000</v>
+        <v>82799000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414941000</v>
+        <v>382121000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1348652000</v>
+        <v>1299865000</v>
       </c>
       <c r="AS2" t="n">
-        <v>5492483000</v>
+        <v>3402951000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6841135000</v>
+        <v>4702816000</v>
       </c>
       <c r="AU2" t="n">
-        <v>6841135000</v>
+        <v>4702816000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-7297729.359348</v>
+        <v>25615118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.221486</v>
+        <v>0.223</v>
       </c>
       <c r="D3" t="n">
-        <v>831428000</v>
+        <v>723413000</v>
       </c>
       <c r="E3" t="n">
-        <v>-32949000</v>
+        <v>114866000</v>
       </c>
       <c r="F3" t="n">
-        <v>-32949000</v>
+        <v>114866000</v>
       </c>
       <c r="G3" t="n">
-        <v>434472000</v>
+        <v>480111000</v>
       </c>
       <c r="H3" t="n">
-        <v>111867000</v>
+        <v>93311000</v>
       </c>
       <c r="I3" t="n">
-        <v>5284415000</v>
+        <v>4983196000</v>
       </c>
       <c r="J3" t="n">
-        <v>798479000</v>
+        <v>838279000</v>
       </c>
       <c r="K3" t="n">
-        <v>686612000</v>
+        <v>744968000</v>
       </c>
       <c r="L3" t="n">
-        <v>9854000</v>
+        <v>16352000</v>
       </c>
       <c r="M3" t="n">
-        <v>5868000</v>
+        <v>4014000</v>
       </c>
       <c r="N3" t="n">
-        <v>15722000</v>
+        <v>20366000</v>
       </c>
       <c r="O3" t="n">
-        <v>460123270.640652</v>
+        <v>390860118</v>
       </c>
       <c r="P3" t="n">
-        <v>434472000</v>
+        <v>480111000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5849548000</v>
+        <v>5659326000</v>
       </c>
       <c r="R3" t="n">
-        <v>1749220000</v>
+        <v>1750727000</v>
       </c>
       <c r="S3" t="n">
-        <v>1749220000</v>
+        <v>1750727000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2484</v>
+        <v>0.2742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2484</v>
+        <v>0.2742</v>
       </c>
       <c r="V3" t="n">
-        <v>434472000</v>
+        <v>480111000</v>
       </c>
       <c r="W3" t="n">
-        <v>434472000</v>
+        <v>480111000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>434472000</v>
+        <v>480111000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-95497000</v>
+        <v>-95781000</v>
       </c>
       <c r="AA3" t="n">
-        <v>529969000</v>
+        <v>575892000</v>
       </c>
       <c r="AB3" t="n">
-        <v>529969000</v>
+        <v>575892000</v>
       </c>
       <c r="AC3" t="n">
-        <v>150775000</v>
+        <v>165062000</v>
       </c>
       <c r="AD3" t="n">
-        <v>680744000</v>
+        <v>740954000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-587000</v>
+        <v>2175000</v>
       </c>
       <c r="AF3" t="n">
-        <v>154000</v>
+        <v>-170000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-154000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>170000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>157424000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>9854000</v>
+        <v>16352000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5868000</v>
+        <v>4014000</v>
       </c>
       <c r="AK3" t="n">
-        <v>15722000</v>
+        <v>20366000</v>
       </c>
       <c r="AL3" t="n">
-        <v>687875000</v>
+        <v>617153000</v>
       </c>
       <c r="AM3" t="n">
-        <v>565133000</v>
+        <v>676130000</v>
       </c>
       <c r="AN3" t="n">
-        <v>46113000</v>
+        <v>157424000</v>
       </c>
       <c r="AO3" t="n">
-        <v>566488000</v>
+        <v>563609000</v>
       </c>
       <c r="AP3" t="n">
-        <v>94282000</v>
+        <v>100078000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>472206000</v>
+        <v>463531000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1253008000</v>
+        <v>1293283000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5284415000</v>
+        <v>4983196000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6537423000</v>
+        <v>6276479000</v>
       </c>
       <c r="AU3" t="n">
-        <v>6537423000</v>
+        <v>6276479000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>25615118</v>
+        <v>-7297729.359348</v>
       </c>
       <c r="C4" t="n">
-        <v>0.223</v>
+        <v>0.221486</v>
       </c>
       <c r="D4" t="n">
-        <v>723413000</v>
+        <v>831428000</v>
       </c>
       <c r="E4" t="n">
-        <v>114866000</v>
+        <v>-32949000</v>
       </c>
       <c r="F4" t="n">
-        <v>114866000</v>
+        <v>-32949000</v>
       </c>
       <c r="G4" t="n">
-        <v>480111000</v>
+        <v>434472000</v>
       </c>
       <c r="H4" t="n">
-        <v>93311000</v>
+        <v>111867000</v>
       </c>
       <c r="I4" t="n">
-        <v>4983196000</v>
+        <v>5284415000</v>
       </c>
       <c r="J4" t="n">
-        <v>838279000</v>
+        <v>798479000</v>
       </c>
       <c r="K4" t="n">
-        <v>744968000</v>
+        <v>686612000</v>
       </c>
       <c r="L4" t="n">
-        <v>16352000</v>
+        <v>9854000</v>
       </c>
       <c r="M4" t="n">
-        <v>4014000</v>
+        <v>5868000</v>
       </c>
       <c r="N4" t="n">
-        <v>20366000</v>
+        <v>15722000</v>
       </c>
       <c r="O4" t="n">
-        <v>390860118</v>
+        <v>460123270.640652</v>
       </c>
       <c r="P4" t="n">
-        <v>480111000</v>
+        <v>434472000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5659326000</v>
+        <v>5849548000</v>
       </c>
       <c r="R4" t="n">
-        <v>1750727000</v>
+        <v>1749220000</v>
       </c>
       <c r="S4" t="n">
-        <v>1750727000</v>
+        <v>1749220000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2742</v>
+        <v>0.2484</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2742</v>
+        <v>0.2484</v>
       </c>
       <c r="V4" t="n">
-        <v>480111000</v>
+        <v>434472000</v>
       </c>
       <c r="W4" t="n">
-        <v>480111000</v>
+        <v>434472000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>480111000</v>
+        <v>434472000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-95781000</v>
+        <v>-95497000</v>
       </c>
       <c r="AA4" t="n">
-        <v>575892000</v>
+        <v>529969000</v>
       </c>
       <c r="AB4" t="n">
-        <v>575892000</v>
+        <v>529969000</v>
       </c>
       <c r="AC4" t="n">
-        <v>165062000</v>
+        <v>150775000</v>
       </c>
       <c r="AD4" t="n">
-        <v>740954000</v>
+        <v>680744000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2175000</v>
+        <v>-587000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-170000</v>
+        <v>154000</v>
       </c>
       <c r="AG4" t="n">
-        <v>170000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>157424000</v>
-      </c>
+        <v>-154000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>16352000</v>
+        <v>9854000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4014000</v>
+        <v>5868000</v>
       </c>
       <c r="AK4" t="n">
-        <v>20366000</v>
+        <v>15722000</v>
       </c>
       <c r="AL4" t="n">
-        <v>617153000</v>
+        <v>687875000</v>
       </c>
       <c r="AM4" t="n">
-        <v>676130000</v>
+        <v>565133000</v>
       </c>
       <c r="AN4" t="n">
-        <v>157424000</v>
+        <v>46113000</v>
       </c>
       <c r="AO4" t="n">
-        <v>563609000</v>
+        <v>566488000</v>
       </c>
       <c r="AP4" t="n">
-        <v>100078000</v>
+        <v>94282000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>463531000</v>
+        <v>472206000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1293283000</v>
+        <v>1253008000</v>
       </c>
       <c r="AS4" t="n">
-        <v>4983196000</v>
+        <v>5284415000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6276479000</v>
+        <v>6537423000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6276479000</v>
+        <v>6537423000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>12159521</v>
+        <v>-7059534.771645</v>
       </c>
       <c r="C5" t="n">
-        <v>0.223</v>
+        <v>0.221406</v>
       </c>
       <c r="D5" t="n">
-        <v>913810000</v>
+        <v>879519000</v>
       </c>
       <c r="E5" t="n">
-        <v>54527000</v>
+        <v>-31885000</v>
       </c>
       <c r="F5" t="n">
-        <v>54527000</v>
+        <v>-31885000</v>
       </c>
       <c r="G5" t="n">
-        <v>617014000</v>
+        <v>477996000</v>
       </c>
       <c r="H5" t="n">
-        <v>73438000</v>
+        <v>85014000</v>
       </c>
       <c r="I5" t="n">
-        <v>3402951000</v>
+        <v>5492483000</v>
       </c>
       <c r="J5" t="n">
-        <v>968337000</v>
+        <v>847634000</v>
       </c>
       <c r="K5" t="n">
-        <v>894899000</v>
+        <v>762620000</v>
       </c>
       <c r="L5" t="n">
-        <v>36167000</v>
+        <v>18628000</v>
       </c>
       <c r="M5" t="n">
-        <v>3486000</v>
+        <v>3165000</v>
       </c>
       <c r="N5" t="n">
-        <v>39653000</v>
+        <v>21793000</v>
       </c>
       <c r="O5" t="n">
-        <v>574646521</v>
+        <v>502821465.228355</v>
       </c>
       <c r="P5" t="n">
-        <v>617014000</v>
+        <v>477996000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3894653000</v>
+        <v>6060086000</v>
       </c>
       <c r="R5" t="n">
-        <v>1684301000</v>
+        <v>1732820000</v>
       </c>
       <c r="S5" t="n">
-        <v>1684301000</v>
+        <v>1732820000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3663</v>
+        <v>0.2758</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3663</v>
+        <v>0.2758</v>
       </c>
       <c r="V5" t="n">
-        <v>617014000</v>
+        <v>477996000</v>
       </c>
       <c r="W5" t="n">
-        <v>617014000</v>
+        <v>477996000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>617014000</v>
+        <v>477996000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-75521000</v>
+        <v>-113311000</v>
       </c>
       <c r="AA5" t="n">
-        <v>692535000</v>
+        <v>591307000</v>
       </c>
       <c r="AB5" t="n">
-        <v>692535000</v>
+        <v>591307000</v>
       </c>
       <c r="AC5" t="n">
-        <v>198878000</v>
+        <v>168148000</v>
       </c>
       <c r="AD5" t="n">
-        <v>891413000</v>
+        <v>759455000</v>
       </c>
       <c r="AE5" t="n">
-        <v>3399000</v>
+        <v>-1090000</v>
       </c>
       <c r="AF5" t="n">
-        <v>43000</v>
+        <v>-1315000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-43000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>62220000</v>
-      </c>
+        <v>1315000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>36167000</v>
+        <v>18628000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3486000</v>
+        <v>3165000</v>
       </c>
       <c r="AK5" t="n">
-        <v>39653000</v>
+        <v>21793000</v>
       </c>
       <c r="AL5" t="n">
-        <v>808163000</v>
+        <v>781049000</v>
       </c>
       <c r="AM5" t="n">
-        <v>491702000</v>
+        <v>567603000</v>
       </c>
       <c r="AN5" t="n">
-        <v>62220000</v>
+        <v>74150000</v>
       </c>
       <c r="AO5" t="n">
-        <v>464920000</v>
+        <v>516705000</v>
       </c>
       <c r="AP5" t="n">
-        <v>82799000</v>
+        <v>101764000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>382121000</v>
+        <v>414941000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1299865000</v>
+        <v>1348652000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3402951000</v>
+        <v>5492483000</v>
       </c>
       <c r="AT5" t="n">
-        <v>4702816000</v>
+        <v>6841135000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4702816000</v>
+        <v>6841135000</v>
       </c>
     </row>
   </sheetData>
@@ -1591,261 +1591,263 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1728554000</v>
+        <v>1753920000</v>
       </c>
       <c r="D2" t="n">
-        <v>1728554000</v>
+        <v>1753920000</v>
       </c>
       <c r="E2" t="n">
-        <v>45818000</v>
+        <v>21829000</v>
       </c>
       <c r="F2" t="n">
-        <v>3215398000</v>
+        <v>2728419000</v>
       </c>
       <c r="G2" t="n">
-        <v>5036674000</v>
+        <v>4445213000</v>
       </c>
       <c r="H2" t="n">
-        <v>2222447000</v>
+        <v>2890858000</v>
       </c>
       <c r="I2" t="n">
-        <v>3215398000</v>
+        <v>2728419000</v>
       </c>
       <c r="J2" t="n">
-        <v>10270000</v>
+        <v>20429000</v>
       </c>
       <c r="K2" t="n">
-        <v>5001126000</v>
+        <v>4443813000</v>
       </c>
       <c r="L2" t="n">
-        <v>5001431000</v>
+        <v>4443813000</v>
       </c>
       <c r="M2" t="n">
-        <v>5386041000</v>
+        <v>4691738000</v>
       </c>
       <c r="N2" t="n">
-        <v>384915000</v>
+        <v>247925000</v>
       </c>
       <c r="O2" t="n">
-        <v>5001126000</v>
+        <v>4443813000</v>
       </c>
       <c r="P2" t="n">
+        <v>5714000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1283408000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3131888000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15519000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15519000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2574754000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>136974000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>20787000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>107008000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9179000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9179000</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2518048000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2291136000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>15291000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>15291000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3830612000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>78081000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>75204000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2877000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2572000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>305000</v>
-      </c>
       <c r="AB2" t="n">
-        <v>3752531000</v>
+        <v>2437780000</v>
       </c>
       <c r="AC2" t="n">
-        <v>138027000</v>
+        <v>135072000</v>
       </c>
       <c r="AD2" t="n">
-        <v>42941000</v>
+        <v>12650000</v>
       </c>
       <c r="AE2" t="n">
-        <v>7698000</v>
+        <v>11250000</v>
       </c>
       <c r="AF2" t="n">
-        <v>35243000</v>
+        <v>1400000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1848000</v>
+        <v>2878000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2629640000</v>
+        <v>586364000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1155841000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>986502000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2580000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>166262000</v>
+        <v>249459000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1307537000</v>
+        <v>586364000</v>
       </c>
       <c r="AM2" t="n">
-        <v>9216653000</v>
+        <v>7266492000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3241675000</v>
+        <v>1937854000</v>
       </c>
       <c r="AO2" t="n">
-        <v>374525000</v>
+        <v>367000</v>
       </c>
       <c r="AP2" t="n">
-        <v>45719000</v>
+        <v>12663000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>110903000</v>
+        <v>38196000</v>
       </c>
       <c r="AR2" t="n">
-        <v>277046000</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>277046000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1854000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1854000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>549125000</v>
+        <v>58970000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1785728000</v>
+        <v>1715394000</v>
       </c>
       <c r="AX2" t="n">
-        <v>297557000</v>
+        <v>371687000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1488171000</v>
+        <v>1343707000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>96775000</v>
+        <v>112264000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-191031000</v>
+        <v>-76686000</v>
       </c>
       <c r="BB2" t="n">
-        <v>287806000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
+        <v>188950000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>367000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>112264000</v>
+      </c>
       <c r="BE2" t="n">
-        <v>145222000</v>
+        <v>80733000</v>
       </c>
       <c r="BF2" t="n">
-        <v>142584000</v>
+        <v>108217000</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>5974978000</v>
+        <v>5328638000</v>
       </c>
       <c r="BI2" t="n">
-        <v>20493000</v>
+        <v>4474000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>67422000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>11119000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>65589000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>1540000</v>
+        <v>3549000</v>
       </c>
       <c r="BM2" t="n">
-        <v>477867000</v>
+        <v>426815000</v>
       </c>
       <c r="BN2" t="n">
-        <v>2785875000</v>
+        <v>897635000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2621781000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>3935000</v>
-      </c>
+        <v>3985046000</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>2617846000</v>
+        <v>3985046000</v>
       </c>
       <c r="BR2" t="n">
-        <v>6000000</v>
+        <v>155000000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2611846000</v>
+        <v>3830046000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1749220000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1749220000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>102325000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2787095000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4672110000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1836226000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2787095000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26162000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4595947000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4644004000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4832654000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>236707000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4595947000</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>1743878000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1743878000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>63747000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3066401000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4918017000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1945750000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3066401000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18796000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4873066000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4877248000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5213634000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>340568000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4873066000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6143000</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2089887000</v>
+        <v>1715682000</v>
       </c>
       <c r="R3" t="n">
-        <v>2647026000</v>
+        <v>2798236000</v>
       </c>
       <c r="S3" t="n">
         <v>15480000</v>
@@ -1854,207 +1856,207 @@
         <v>15480000</v>
       </c>
       <c r="U3" t="n">
-        <v>3615609000</v>
+        <v>3210473000</v>
       </c>
       <c r="V3" t="n">
-        <v>103903000</v>
+        <v>166739000</v>
       </c>
       <c r="W3" t="n">
-        <v>9322000</v>
+        <v>13174000</v>
       </c>
       <c r="X3" t="n">
-        <v>82451000</v>
+        <v>90565000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12130000</v>
+        <v>63000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>7948000</v>
+        <v>14943000</v>
       </c>
       <c r="AA3" t="n">
-        <v>4182000</v>
+        <v>48057000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3511706000</v>
+        <v>3043734000</v>
       </c>
       <c r="AC3" t="n">
-        <v>103965000</v>
+        <v>104932000</v>
       </c>
       <c r="AD3" t="n">
-        <v>51617000</v>
+        <v>39325000</v>
       </c>
       <c r="AE3" t="n">
-        <v>10848000</v>
+        <v>11219000</v>
       </c>
       <c r="AF3" t="n">
-        <v>40769000</v>
+        <v>28106000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1366000</v>
+        <v>2195000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2484420000</v>
+        <v>2228097000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1193151000</v>
+        <v>1089754000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>7147000</v>
       </c>
       <c r="AK3" t="n">
-        <v>140978000</v>
+        <v>129033000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1150291000</v>
+        <v>1002163000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8829243000</v>
+        <v>8043127000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3371787000</v>
+        <v>3163167000</v>
       </c>
       <c r="AO3" t="n">
-        <v>399230000</v>
+        <v>204056000</v>
       </c>
       <c r="AP3" t="n">
-        <v>38009000</v>
+        <v>10893000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>83323000</v>
+        <v>68134000</v>
       </c>
       <c r="AR3" t="n">
-        <v>362663000</v>
+        <v>384440000</v>
       </c>
       <c r="AS3" t="n">
-        <v>362663000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
+        <v>384440000</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>558480000</v>
+        <v>556684000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1806665000</v>
+        <v>1808852000</v>
       </c>
       <c r="AX3" t="n">
-        <v>318494000</v>
+        <v>354196000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1488171000</v>
+        <v>1454656000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>123417000</v>
+        <v>130108000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-156754000</v>
+        <v>-115012000</v>
       </c>
       <c r="BB3" t="n">
-        <v>280171000</v>
+        <v>245120000</v>
       </c>
       <c r="BC3" t="n">
-        <v>378000</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>400000</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>129708000</v>
+      </c>
       <c r="BE3" t="n">
-        <v>136280000</v>
+        <v>114063000</v>
       </c>
       <c r="BF3" t="n">
-        <v>143891000</v>
+        <v>130657000</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>5457456000</v>
+        <v>4879960000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3661000</v>
+        <v>11561000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>38165000</v>
+        <v>29288000</v>
       </c>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>3191000</v>
+        <v>2985000</v>
       </c>
       <c r="BM3" t="n">
-        <v>617867000</v>
+        <v>1286131000</v>
       </c>
       <c r="BN3" t="n">
-        <v>2448798000</v>
+        <v>2000031000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2345774000</v>
+        <v>1549964000</v>
       </c>
       <c r="BP3" t="n">
-        <v>4264000</v>
+        <v>15590000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2341510000</v>
+        <v>1534374000</v>
       </c>
       <c r="BR3" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>2335510000</v>
+        <v>1534374000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>1749220000</v>
+        <v>1743878000</v>
       </c>
       <c r="D4" t="n">
-        <v>1749220000</v>
+        <v>1743878000</v>
       </c>
       <c r="E4" t="n">
-        <v>102325000</v>
+        <v>63747000</v>
       </c>
       <c r="F4" t="n">
-        <v>2787095000</v>
+        <v>3066401000</v>
       </c>
       <c r="G4" t="n">
-        <v>4672110000</v>
+        <v>4918017000</v>
       </c>
       <c r="H4" t="n">
-        <v>1836226000</v>
+        <v>1945750000</v>
       </c>
       <c r="I4" t="n">
-        <v>2787095000</v>
+        <v>3066401000</v>
       </c>
       <c r="J4" t="n">
-        <v>26162000</v>
+        <v>18796000</v>
       </c>
       <c r="K4" t="n">
-        <v>4595947000</v>
+        <v>4873066000</v>
       </c>
       <c r="L4" t="n">
-        <v>4644004000</v>
+        <v>4877248000</v>
       </c>
       <c r="M4" t="n">
-        <v>4832654000</v>
+        <v>5213634000</v>
       </c>
       <c r="N4" t="n">
-        <v>236707000</v>
+        <v>340568000</v>
       </c>
       <c r="O4" t="n">
-        <v>4595947000</v>
+        <v>4873066000</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6143000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1715682000</v>
+        <v>2089887000</v>
       </c>
       <c r="R4" t="n">
-        <v>2798236000</v>
+        <v>2647026000</v>
       </c>
       <c r="S4" t="n">
         <v>15480000</v>
@@ -2063,358 +2065,356 @@
         <v>15480000</v>
       </c>
       <c r="U4" t="n">
-        <v>3210473000</v>
+        <v>3615609000</v>
       </c>
       <c r="V4" t="n">
-        <v>166739000</v>
+        <v>103903000</v>
       </c>
       <c r="W4" t="n">
-        <v>13174000</v>
+        <v>9322000</v>
       </c>
       <c r="X4" t="n">
-        <v>90565000</v>
+        <v>82451000</v>
       </c>
       <c r="Y4" t="n">
-        <v>63000000</v>
+        <v>12130000</v>
       </c>
       <c r="Z4" t="n">
-        <v>14943000</v>
+        <v>7948000</v>
       </c>
       <c r="AA4" t="n">
-        <v>48057000</v>
+        <v>4182000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3043734000</v>
+        <v>3511706000</v>
       </c>
       <c r="AC4" t="n">
-        <v>104932000</v>
+        <v>103965000</v>
       </c>
       <c r="AD4" t="n">
-        <v>39325000</v>
+        <v>51617000</v>
       </c>
       <c r="AE4" t="n">
-        <v>11219000</v>
+        <v>10848000</v>
       </c>
       <c r="AF4" t="n">
-        <v>28106000</v>
+        <v>40769000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2195000</v>
+        <v>1366000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2228097000</v>
+        <v>2484420000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1089754000</v>
+        <v>1193151000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7147000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>129033000</v>
+        <v>140978000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1002163000</v>
+        <v>1150291000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8043127000</v>
+        <v>8829243000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3163167000</v>
+        <v>3371787000</v>
       </c>
       <c r="AO4" t="n">
-        <v>204056000</v>
+        <v>399230000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10893000</v>
+        <v>38009000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>68134000</v>
+        <v>83323000</v>
       </c>
       <c r="AR4" t="n">
-        <v>384440000</v>
+        <v>362663000</v>
       </c>
       <c r="AS4" t="n">
-        <v>384440000</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+        <v>362663000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
       <c r="AV4" t="n">
-        <v>556684000</v>
+        <v>558480000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1808852000</v>
+        <v>1806665000</v>
       </c>
       <c r="AX4" t="n">
-        <v>354196000</v>
+        <v>318494000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1454656000</v>
+        <v>1488171000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>130108000</v>
+        <v>123417000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-115012000</v>
+        <v>-156754000</v>
       </c>
       <c r="BB4" t="n">
-        <v>245120000</v>
+        <v>280171000</v>
       </c>
       <c r="BC4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>129708000</v>
-      </c>
+        <v>378000</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>114063000</v>
+        <v>136280000</v>
       </c>
       <c r="BF4" t="n">
-        <v>130657000</v>
+        <v>143891000</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>4879960000</v>
+        <v>5457456000</v>
       </c>
       <c r="BI4" t="n">
-        <v>11561000</v>
+        <v>3661000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>29288000</v>
+        <v>38165000</v>
       </c>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>2985000</v>
+        <v>3191000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1286131000</v>
+        <v>617867000</v>
       </c>
       <c r="BN4" t="n">
-        <v>2000031000</v>
+        <v>2448798000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1549964000</v>
+        <v>2345774000</v>
       </c>
       <c r="BP4" t="n">
-        <v>15590000</v>
+        <v>4264000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1534374000</v>
+        <v>2341510000</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1534374000</v>
+        <v>2335510000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1753920000</v>
+        <v>1728554000</v>
       </c>
       <c r="D5" t="n">
-        <v>1753920000</v>
+        <v>1728554000</v>
       </c>
       <c r="E5" t="n">
-        <v>21829000</v>
+        <v>45818000</v>
       </c>
       <c r="F5" t="n">
-        <v>2728419000</v>
+        <v>3215398000</v>
       </c>
       <c r="G5" t="n">
-        <v>4445213000</v>
+        <v>5036674000</v>
       </c>
       <c r="H5" t="n">
-        <v>2890858000</v>
+        <v>2222447000</v>
       </c>
       <c r="I5" t="n">
-        <v>2728419000</v>
+        <v>3215398000</v>
       </c>
       <c r="J5" t="n">
-        <v>20429000</v>
+        <v>10270000</v>
       </c>
       <c r="K5" t="n">
-        <v>4443813000</v>
+        <v>5001126000</v>
       </c>
       <c r="L5" t="n">
-        <v>4443813000</v>
+        <v>5001431000</v>
       </c>
       <c r="M5" t="n">
-        <v>4691738000</v>
+        <v>5386041000</v>
       </c>
       <c r="N5" t="n">
-        <v>247925000</v>
+        <v>384915000</v>
       </c>
       <c r="O5" t="n">
-        <v>4443813000</v>
+        <v>5001126000</v>
       </c>
       <c r="P5" t="n">
-        <v>5714000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1283408000</v>
+        <v>2518048000</v>
       </c>
       <c r="R5" t="n">
-        <v>3131888000</v>
+        <v>2291136000</v>
       </c>
       <c r="S5" t="n">
-        <v>15519000</v>
+        <v>15291000</v>
       </c>
       <c r="T5" t="n">
-        <v>15519000</v>
+        <v>15291000</v>
       </c>
       <c r="U5" t="n">
-        <v>2574754000</v>
+        <v>3830612000</v>
       </c>
       <c r="V5" t="n">
-        <v>136974000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>20787000</v>
-      </c>
+        <v>78081000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>107008000</v>
+        <v>75204000</v>
       </c>
       <c r="Y5" t="n">
-        <v>9179000</v>
+        <v>2877000</v>
       </c>
       <c r="Z5" t="n">
-        <v>9179000</v>
+        <v>2572000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>305000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2437780000</v>
+        <v>3752531000</v>
       </c>
       <c r="AC5" t="n">
-        <v>135072000</v>
+        <v>138027000</v>
       </c>
       <c r="AD5" t="n">
-        <v>12650000</v>
+        <v>42941000</v>
       </c>
       <c r="AE5" t="n">
-        <v>11250000</v>
+        <v>7698000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1400000</v>
+        <v>35243000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2878000</v>
+        <v>1848000</v>
       </c>
       <c r="AH5" t="n">
-        <v>586364000</v>
+        <v>2629640000</v>
       </c>
       <c r="AI5" t="n">
-        <v>986502000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2580000</v>
-      </c>
+        <v>1155841000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>249459000</v>
+        <v>166262000</v>
       </c>
       <c r="AL5" t="n">
-        <v>586364000</v>
+        <v>1307537000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7266492000</v>
+        <v>9216653000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1937854000</v>
+        <v>3241675000</v>
       </c>
       <c r="AO5" t="n">
-        <v>367000</v>
+        <v>374525000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12663000</v>
+        <v>45719000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>38196000</v>
+        <v>110903000</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>277046000</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+        <v>277046000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1854000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1854000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>58970000</v>
+        <v>549125000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1715394000</v>
+        <v>1785728000</v>
       </c>
       <c r="AX5" t="n">
-        <v>371687000</v>
+        <v>297557000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1343707000</v>
+        <v>1488171000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>112264000</v>
+        <v>96775000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-76686000</v>
+        <v>-191031000</v>
       </c>
       <c r="BB5" t="n">
-        <v>188950000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>367000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>112264000</v>
-      </c>
+        <v>287806000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>80733000</v>
+        <v>145222000</v>
       </c>
       <c r="BF5" t="n">
-        <v>108217000</v>
+        <v>142584000</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>5328638000</v>
+        <v>5974978000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4474000</v>
+        <v>20493000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11119000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>65589000</v>
-      </c>
+        <v>67422000</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>3549000</v>
+        <v>1540000</v>
       </c>
       <c r="BM5" t="n">
-        <v>426815000</v>
+        <v>477867000</v>
       </c>
       <c r="BN5" t="n">
-        <v>897635000</v>
+        <v>2785875000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3985046000</v>
-      </c>
-      <c r="BP5" t="inlineStr"/>
+        <v>2621781000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3935000</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>3985046000</v>
+        <v>2617846000</v>
       </c>
       <c r="BR5" t="n">
-        <v>155000000</v>
+        <v>6000000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3830046000</v>
+        <v>2611846000</v>
       </c>
     </row>
   </sheetData>
@@ -2730,714 +2730,714 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>637183000</v>
+        <v>777394000</v>
       </c>
       <c r="C2" t="n">
-        <v>-20631000</v>
+        <v>-5714000</v>
       </c>
       <c r="D2" t="n">
-        <v>-46725000</v>
+        <v>-6203000</v>
       </c>
       <c r="E2" t="n">
-        <v>34500000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1086151000</v>
+      </c>
       <c r="G2" t="n">
-        <v>-47625000</v>
+        <v>-59614000</v>
       </c>
       <c r="H2" t="n">
-        <v>2617846000</v>
+        <v>3985046000</v>
       </c>
       <c r="I2" t="n">
-        <v>2341510000</v>
+        <v>3170589000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2940000</v>
+        <v>-13648000</v>
       </c>
       <c r="K2" t="n">
-        <v>279276000</v>
+        <v>828105000</v>
       </c>
       <c r="L2" t="n">
-        <v>-444304000</v>
+        <v>908093000</v>
       </c>
       <c r="M2" t="n">
-        <v>6390000</v>
+        <v>33640000</v>
       </c>
       <c r="N2" t="n">
-        <v>-3165000</v>
+        <v>-1534000</v>
       </c>
       <c r="O2" t="n">
-        <v>-402306000</v>
+        <v>-166435000</v>
       </c>
       <c r="P2" t="n">
-        <v>-402306000</v>
+        <v>-166435000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-20631000</v>
+        <v>1080437000</v>
       </c>
       <c r="R2" t="n">
-        <v>-20631000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>-5714000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1086151000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-12225000</v>
+        <v>-6203000</v>
       </c>
       <c r="U2" t="n">
-        <v>-12225000</v>
+        <v>-6203000</v>
       </c>
       <c r="V2" t="n">
-        <v>-46725000</v>
+        <v>-6203000</v>
       </c>
       <c r="W2" t="n">
-        <v>34500000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>38772000</v>
+        <v>-916996000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1540000</v>
+        <v>-4195000</v>
       </c>
       <c r="Z2" t="n">
-        <v>21793000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9449000</v>
-      </c>
+        <v>39653000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>55376000</v>
+        <v>84484000</v>
       </c>
       <c r="AC2" t="n">
-        <v>272376000</v>
+        <v>3387984000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-217000000</v>
+        <v>-3303500000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1793000</v>
+        <v>2912000</v>
       </c>
       <c r="AF2" t="n">
+        <v>2912000</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" t="n">
-        <v>-1793000</v>
-      </c>
       <c r="AH2" t="n">
-        <v>-3018000</v>
+        <v>-980485000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-3018000</v>
+        <v>-1080485000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-21223000</v>
+        <v>-22980000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-21223000</v>
+        <v>-22980000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-20272000</v>
+        <v>-36385000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6130000</v>
+        <v>249000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-26402000</v>
+        <v>-36634000</v>
       </c>
       <c r="AP2" t="n">
-        <v>684808000</v>
+        <v>837008000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-160278000</v>
+        <v>-210107000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-94037000</v>
+        <v>99895000</v>
       </c>
       <c r="AS2" t="n">
-        <v>16203000</v>
+        <v>172088000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-19976000</v>
+        <v>294587000</v>
       </c>
       <c r="AU2" t="n">
-        <v>163383000</v>
+        <v>190969000</v>
       </c>
       <c r="AV2" t="n">
-        <v>95336000</v>
+        <v>-226241000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1651000</v>
+        <v>-1779000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-350634000</v>
+        <v>-329729000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-18628000</v>
+        <v>-36167000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>74150000</v>
+        <v>62220000</v>
       </c>
       <c r="BA2" t="n">
-        <v>85014000</v>
+        <v>73438000</v>
       </c>
       <c r="BB2" t="n">
-        <v>42160000</v>
+        <v>40464000</v>
       </c>
       <c r="BC2" t="n">
-        <v>42854000</v>
+        <v>32974000</v>
       </c>
       <c r="BD2" t="n">
-        <v>34851000</v>
+        <v>-61247000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2940000</v>
+        <v>17606000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1169000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>146000</v>
-      </c>
+        <v>-43000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>759455000</v>
+        <v>891413000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>862177000</v>
+        <v>-1066158000</v>
       </c>
       <c r="C3" t="n">
-        <v>-6143000</v>
+        <v>-29859000</v>
       </c>
       <c r="D3" t="n">
-        <v>-93975000</v>
+        <v>-31133000</v>
       </c>
       <c r="E3" t="n">
-        <v>48290000</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>46126000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>-50926000</v>
+        <v>-46441000</v>
       </c>
       <c r="H3" t="n">
-        <v>2341510000</v>
+        <v>1534374000</v>
       </c>
       <c r="I3" t="n">
-        <v>1534374000</v>
+        <v>3985046000</v>
       </c>
       <c r="J3" t="n">
-        <v>-3031000</v>
+        <v>1110000</v>
       </c>
       <c r="K3" t="n">
-        <v>810167000</v>
+        <v>-2451782000</v>
       </c>
       <c r="L3" t="n">
-        <v>-223769000</v>
+        <v>-448456000</v>
       </c>
       <c r="M3" t="n">
-        <v>45854000</v>
+        <v>-2405000</v>
       </c>
       <c r="N3" t="n">
-        <v>-5040000</v>
+        <v>-2357000</v>
       </c>
       <c r="O3" t="n">
-        <v>-199982000</v>
+        <v>-414760000</v>
       </c>
       <c r="P3" t="n">
-        <v>-199982000</v>
+        <v>-414760000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6143000</v>
+        <v>-29859000</v>
       </c>
       <c r="R3" t="n">
-        <v>-6143000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-29859000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="n">
-        <v>-45685000</v>
+        <v>14993000</v>
       </c>
       <c r="U3" t="n">
-        <v>-45685000</v>
+        <v>14993000</v>
       </c>
       <c r="V3" t="n">
-        <v>-93975000</v>
+        <v>-31133000</v>
       </c>
       <c r="W3" t="n">
-        <v>48290000</v>
+        <v>46126000</v>
       </c>
       <c r="X3" t="n">
-        <v>120833000</v>
+        <v>-983609000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-6185000</v>
+        <v>-4503000</v>
       </c>
       <c r="Z3" t="n">
-        <v>15722000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+        <v>21365000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>145243000</v>
+        <v>-382924000</v>
       </c>
       <c r="AC3" t="n">
-        <v>145243000</v>
+        <v>5139666000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-5522590000</v>
       </c>
       <c r="AE3" t="n">
-        <v>5451000</v>
+        <v>-103085000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5758000</v>
+        <v>8058000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-307000</v>
+        <v>-111143000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2395000</v>
+        <v>-471137000</v>
       </c>
       <c r="AI3" t="n">
-        <v>58124000</v>
+        <v>200000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-55729000</v>
+        <v>-671137000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-11993000</v>
+        <v>-11541000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-11993000</v>
+        <v>-11541000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-29800000</v>
+        <v>-31784000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9133000</v>
+        <v>3116000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-38933000</v>
+        <v>-34900000</v>
       </c>
       <c r="AP3" t="n">
-        <v>913103000</v>
+        <v>-1019717000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-177206000</v>
+        <v>-247528000</v>
       </c>
       <c r="AR3" t="n">
-        <v>232706000</v>
+        <v>-1642252000</v>
       </c>
       <c r="AS3" t="n">
-        <v>173060000</v>
+        <v>2349000</v>
       </c>
       <c r="AT3" t="n">
-        <v>104390000</v>
+        <v>87787000</v>
       </c>
       <c r="AU3" t="n">
-        <v>133408000</v>
+        <v>385512000</v>
       </c>
       <c r="AV3" t="n">
-        <v>252894000</v>
+        <v>-1019611000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-206000</v>
+        <v>568000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-430840000</v>
+        <v>-1098857000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-9854000</v>
+        <v>-16352000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>46113000</v>
+        <v>157424000</v>
       </c>
       <c r="BA3" t="n">
-        <v>111867000</v>
+        <v>93311000</v>
       </c>
       <c r="BB3" t="n">
-        <v>54875000</v>
+        <v>50452000</v>
       </c>
       <c r="BC3" t="n">
-        <v>56992000</v>
+        <v>42859000</v>
       </c>
       <c r="BD3" t="n">
-        <v>25856000</v>
+        <v>-116261000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3031000</v>
+        <v>10817000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-154000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
+        <v>170000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>680744000</v>
+        <v>740954000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1066158000</v>
+        <v>862177000</v>
       </c>
       <c r="C4" t="n">
-        <v>-29859000</v>
+        <v>-6143000</v>
       </c>
       <c r="D4" t="n">
-        <v>-31133000</v>
+        <v>-93975000</v>
       </c>
       <c r="E4" t="n">
-        <v>46126000</v>
-      </c>
-      <c r="F4" t="n">
+        <v>48290000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-50926000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2341510000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1534374000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3031000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>810167000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-223769000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45854000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-5040000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-199982000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-199982000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-6143000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-6143000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>-45685000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-45685000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-93975000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>48290000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>120833000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-6185000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15722000</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
-        <v>-46441000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1534374000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3985046000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1110000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-2451782000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-448456000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-2405000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-2357000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-414760000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-414760000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-29859000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-29859000</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
+        <v>145243000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>145243000</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>14993000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14993000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-31133000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>46126000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-983609000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-4503000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>21365000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>-382924000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5139666000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-5522590000</v>
-      </c>
       <c r="AE4" t="n">
-        <v>-103085000</v>
+        <v>5451000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8058000</v>
+        <v>5758000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-111143000</v>
+        <v>-307000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-471137000</v>
+        <v>2395000</v>
       </c>
       <c r="AI4" t="n">
-        <v>200000000</v>
+        <v>58124000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-671137000</v>
+        <v>-55729000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-11541000</v>
+        <v>-11993000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-11541000</v>
+        <v>-11993000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-31784000</v>
+        <v>-29800000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3116000</v>
+        <v>9133000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-34900000</v>
+        <v>-38933000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1019717000</v>
+        <v>913103000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-247528000</v>
+        <v>-177206000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1642252000</v>
+        <v>232706000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2349000</v>
+        <v>173060000</v>
       </c>
       <c r="AT4" t="n">
-        <v>87787000</v>
+        <v>104390000</v>
       </c>
       <c r="AU4" t="n">
-        <v>385512000</v>
+        <v>133408000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1019611000</v>
+        <v>252894000</v>
       </c>
       <c r="AW4" t="n">
-        <v>568000</v>
+        <v>-206000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-1098857000</v>
+        <v>-430840000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-16352000</v>
+        <v>-9854000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>157424000</v>
+        <v>46113000</v>
       </c>
       <c r="BA4" t="n">
-        <v>93311000</v>
+        <v>111867000</v>
       </c>
       <c r="BB4" t="n">
-        <v>50452000</v>
+        <v>54875000</v>
       </c>
       <c r="BC4" t="n">
-        <v>42859000</v>
+        <v>56992000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-116261000</v>
+        <v>25856000</v>
       </c>
       <c r="BE4" t="n">
-        <v>10817000</v>
+        <v>3031000</v>
       </c>
       <c r="BF4" t="n">
-        <v>170000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>-154000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
       <c r="BH4" t="n">
-        <v>740954000</v>
+        <v>680744000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>777394000</v>
+        <v>637183000</v>
       </c>
       <c r="C5" t="n">
-        <v>-5714000</v>
+        <v>-20631000</v>
       </c>
       <c r="D5" t="n">
-        <v>-6203000</v>
+        <v>-46725000</v>
       </c>
       <c r="E5" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-47625000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2617846000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2341510000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-2940000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>279276000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-444304000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6390000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-3165000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-402306000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-402306000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-20631000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-20631000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>-12225000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-12225000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-46725000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>38772000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1540000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>21793000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9449000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>55376000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>272376000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-217000000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1793000</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>1086151000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-59614000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3985046000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3170589000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-13648000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>828105000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>908093000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>33640000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1534000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-166435000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-166435000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1080437000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-5714000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1086151000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-6203000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-6203000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-6203000</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AG5" t="n">
+        <v>-1793000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-3018000</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="n">
-        <v>-916996000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-4195000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39653000</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>84484000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3387984000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-3303500000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2912000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2912000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-980485000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>100000000</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>-1080485000</v>
+        <v>-3018000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-22980000</v>
+        <v>-21223000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-22980000</v>
+        <v>-21223000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-36385000</v>
+        <v>-20272000</v>
       </c>
       <c r="AN5" t="n">
-        <v>249000</v>
+        <v>6130000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-36634000</v>
+        <v>-26402000</v>
       </c>
       <c r="AP5" t="n">
-        <v>837008000</v>
+        <v>684808000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-210107000</v>
+        <v>-160278000</v>
       </c>
       <c r="AR5" t="n">
-        <v>99895000</v>
+        <v>-94037000</v>
       </c>
       <c r="AS5" t="n">
-        <v>172088000</v>
+        <v>16203000</v>
       </c>
       <c r="AT5" t="n">
-        <v>294587000</v>
+        <v>-19976000</v>
       </c>
       <c r="AU5" t="n">
-        <v>190969000</v>
+        <v>163383000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-226241000</v>
+        <v>95336000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1779000</v>
+        <v>1651000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-329729000</v>
+        <v>-350634000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-36167000</v>
+        <v>-18628000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>62220000</v>
+        <v>74150000</v>
       </c>
       <c r="BA5" t="n">
-        <v>73438000</v>
+        <v>85014000</v>
       </c>
       <c r="BB5" t="n">
-        <v>40464000</v>
+        <v>42160000</v>
       </c>
       <c r="BC5" t="n">
-        <v>32974000</v>
+        <v>42854000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-61247000</v>
+        <v>34851000</v>
       </c>
       <c r="BE5" t="n">
-        <v>17606000</v>
+        <v>2940000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-43000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>1169000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>146000</v>
+      </c>
       <c r="BH5" t="n">
-        <v>891413000</v>
+        <v>759455000</v>
       </c>
     </row>
   </sheetData>
@@ -4027,202 +4027,202 @@
       </c>
       <c r="DK1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EY1" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Zhong  Lin', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 7741863, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhubo  Lin', 'age': 44, 'title': 'President &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 3530929, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Di  Zhou', 'age': 48, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 2415350, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xian  Yan', 'title': 'Director of Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Liang', 'age': 41, 'title': 'Vice President of Human Resources', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sim Yee  Oh', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zhong  Lin', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 7735694, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhubo  Lin', 'age': 44, 'title': 'President &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 3528115, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Di  Zhou', 'age': 48, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 2413425, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xian  Yan', 'title': 'Director of Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bin  Liang', 'age': 41, 'title': 'Vice President of Human Resources', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sim Yee  Oh', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4325,34 +4325,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="X2" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
         <v>0.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.17</v>
+        <v>8.75</v>
       </c>
       <c r="AE2" t="n">
         <v>1778803200</v>
@@ -4361,34 +4361,34 @@
         <v>0.48689997</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.793103</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.837937</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2890000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2890000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2734575</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2253548</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2253548</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>6.172414</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5.150599</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>204000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>204000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2707040</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3680489</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3680489</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3073075712</v>
+        <v>2878263296</v>
       </c>
       <c r="AT2" t="n">
-        <v>3090243600</v>
+        <v>2930686920</v>
       </c>
       <c r="AU2" t="n">
         <v>1.64</v>
@@ -4415,19 +4415,19 @@
         <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.4475637</v>
+        <v>0.41919118</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.8776</v>
+        <v>1.8782</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.8299</v>
+        <v>1.8165</v>
       </c>
       <c r="BB2" t="n">
         <v>0.127</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.07055556</v>
+        <v>0.074269004</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>829335616</v>
+        <v>622168576</v>
       </c>
       <c r="BG2" t="n">
         <v>0.06371</v>
@@ -4447,22 +4447,22 @@
         <v>893545971</v>
       </c>
       <c r="BI2" t="n">
-        <v>1716802000</v>
+        <v>1713252000</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.43278</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.032980002</v>
+        <v>0.03311</v>
       </c>
       <c r="BL2" t="n">
-        <v>1716802000</v>
+        <v>1713252000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.4744253</v>
+        <v>3.4725816</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.5151931</v>
+        <v>0.48378992</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4483,19 +4483,19 @@
         <v>0.29</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.3475324</v>
+        <v>0.34725544</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.121</v>
+        <v>0.091</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.082</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.052631557</v>
+        <v>-0.16990292</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.1029</v>
@@ -4509,19 +4509,19 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.5752149</v>
+        <v>2.5736575</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.5752149</v>
+        <v>2.5736575</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.5752149</v>
+        <v>2.5736575</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.5752149</v>
+        <v>2.5736575</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4626,70 +4626,74 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>-0.5555550500000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.039900064</v>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>ES SERVICES</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Ever Sunshine Services Group Limited</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DN2" t="n">
-        <v>-0.021804506</v>
-      </c>
-      <c r="DO2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>finmb_592212037</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-1.7543912</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
         <v>15</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>finmb_592212037</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1780454358</v>
       </c>
       <c r="EB2" t="b">
         <v>0</v>
@@ -4698,11 +4702,11 @@
         <v>1545010200000</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.00999999</v>
+        <v>-0.03000009</v>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>1.79 - 1.82</t>
+          <t>1.66 - 1.71</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
@@ -4711,13 +4715,13 @@
         </is>
       </c>
       <c r="EG2" t="n">
-        <v>2707040</v>
+        <v>2734575</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.14999998</v>
+        <v>0.03999996</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0914634</v>
+        <v>0.02439022</v>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
@@ -4725,13 +4729,13 @@
         </is>
       </c>
       <c r="EK2" t="n">
-        <v>-0.52</v>
+        <v>-0.63</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.22510822</v>
+        <v>-0.27272728</v>
       </c>
       <c r="EM2" t="n">
-        <v>-5.263156</v>
+        <v>-16.990292</v>
       </c>
       <c r="EN2" t="n">
         <v>1756292340</v>
@@ -4746,29 +4750,25 @@
         <v>0.29</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.3475324</v>
+        <v>0.34725544</v>
       </c>
       <c r="ES2" t="n">
         <v>0.28</v>
       </c>
       <c r="ET2" t="n">
-        <v>6.392857</v>
+        <v>6</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0.08759999</v>
+        <v>-0.1982001</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0.0466553</v>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>ES SERVICES</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>Ever Sunshine Services Group Limited</t>
-        </is>
+        <v>-0.10552662</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.1365</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>-0.075144514</v>
       </c>
       <c r="EY2" t="inlineStr"/>
     </row>
